--- a/Switch wiring.xlsx
+++ b/Switch wiring.xlsx
@@ -3687,12 +3687,7 @@
       <c r="F51" s="5">
         <v>4</v>
       </c>
-      <c r="G51" t="s">
-        <v>36</v>
-      </c>
-      <c r="H51" s="5">
-        <v>4</v>
-      </c>
+      <c r="H51" s="5"/>
       <c r="J51" s="5"/>
       <c r="L51">
         <v>0.8433</v>
@@ -4724,7 +4719,12 @@
       <c r="H85" s="5">
         <v>1</v>
       </c>
-      <c r="J85" s="5"/>
+      <c r="I85" t="s">
+        <v>36</v>
+      </c>
+      <c r="J85" s="5">
+        <v>4</v>
+      </c>
       <c r="K85" s="2"/>
       <c r="L85">
         <v>0.69293</v>

--- a/Switch wiring.xlsx
+++ b/Switch wiring.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Switch Positions" sheetId="1" state="visible" r:id="rId2"/>
@@ -85,13 +85,13 @@
     <t>1</t>
   </si>
   <si>
+    <t xml:space="preserve">Laundry near external door</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>Powder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laundry near external door</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t xml:space="preserve">Server Room</t>
@@ -1162,7 +1162,7 @@
     <col customWidth="1" min="7" max="7" width="3.1640625"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="14.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>0.13854</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="14.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1236,7 +1236,7 @@
         <v>0.32571</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="14.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>0.33459</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="14.25">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>0.33463999999999999</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="14.25">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>0.24379000000000001</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="14.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>0.16880000000000001</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="14.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>0.33471000000000001</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="14.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>0.34478999999999999</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="14.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>0.27911000000000002</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>0.16669</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="14.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1461,13 +1461,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>0.51398999999999995</v>
@@ -1476,21 +1476,21 @@
         <v>0.25863000000000003</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="14.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0.51914000000000005</v>
@@ -1499,7 +1499,7 @@
         <v>0.11531</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="14.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -1528,7 +1528,7 @@
         <v>0.34012999999999999</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="14.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1551,7 +1551,7 @@
         <v>0.25028</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="14.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>0.16758999999999999</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="14.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>0.16900999999999999</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="14.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>0.33189999999999997</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="14.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>0.64825999999999995</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="14.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>0.37885999999999997</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="14.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>0.37674000000000002</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="14.25">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>0.69291000000000003</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="14.25">
       <c r="A23" s="3" t="s">
         <v>32</v>
       </c>
@@ -1739,7 +1739,7 @@
         <v>0.39116000000000001</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="14.25">
       <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0.55698000000000003</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="14.25">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -1795,7 +1795,7 @@
         <v>0.75890000000000002</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="14.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>0.78771000000000002</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="14.25">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="6">
         <v>1</v>
@@ -2408,7 +2408,7 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="6">
         <v>2</v>
@@ -2707,7 +2707,7 @@
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F20" s="6">
         <v>1</v>
@@ -2835,7 +2835,7 @@
         <v>3</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H24">
         <v>2</v>
@@ -3696,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H52" s="6">
         <v>0</v>
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H57" s="6">
         <v>0</v>
@@ -4141,7 +4141,7 @@
         <v>21</v>
       </c>
       <c r="E67" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F67" s="6">
         <v>0</v>
@@ -4629,7 +4629,7 @@
         <v>3</v>
       </c>
       <c r="D83">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E83" t="s">
         <v>24</v>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H94" s="6">
         <v>0</v>

--- a/Switch wiring.xlsx
+++ b/Switch wiring.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Switch Positions" sheetId="1" state="visible" r:id="rId2"/>
@@ -12,8 +12,8 @@
     <sheet name="Map Layout" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase">Lights!$A$1:$K$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Lights!$A$1:$K$101</definedName>
+    <definedName name="_xlnm._FilterDatabase">Lights!$A$1:$K$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Lights!$A$1:$K$104</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t xml:space="preserve">Light Fitting</t>
   </si>
@@ -184,6 +184,9 @@
     <t xml:space="preserve">brewery under table</t>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t xml:space="preserve">Bruce office 2 (near stairs)</t>
   </si>
   <si>
@@ -286,6 +289,15 @@
     <t xml:space="preserve">Cellar interior</t>
   </si>
   <si>
+    <t xml:space="preserve">Light above cabinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side Door Strike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side Entry</t>
+  </si>
+  <si>
     <t xml:space="preserve">Master bath towel rail heater</t>
   </si>
   <si>
@@ -361,9 +373,6 @@
     <t xml:space="preserve">B studio exterior east</t>
   </si>
   <si>
-    <t xml:space="preserve">Side Entry</t>
-  </si>
-  <si>
     <t xml:space="preserve">M studio 1 spot</t>
   </si>
   <si>
@@ -373,6 +382,18 @@
     <t xml:space="preserve">B Studio</t>
   </si>
   <si>
+    <t xml:space="preserve">Collision ???</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back Deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collision </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple devices?</t>
+  </si>
+  <si>
     <t xml:space="preserve">M studio 2 bar</t>
   </si>
   <si>
@@ -406,151 +427,160 @@
     <t xml:space="preserve">M studio 1 bar</t>
   </si>
   <si>
+    <t xml:space="preserve">Master Bath sconce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laundry near door</t>
+  </si>
+  <si>
+    <t>Collision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front Door Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collision with Laundry</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bath2 ceiling</t>
   </si>
   <si>
-    <t xml:space="preserve">Laundry near door</t>
+    <t xml:space="preserve">Spot on Curtain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collision with Bath2 soap holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bath2 soap holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchen near laundry</t>
+  </si>
+  <si>
+    <t>Kitchen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed3 Ceiling near door</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master toilet ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hall 3 (wide angle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed2 Ceiling near door</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Bed WIR near bath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Bed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed2 Sconce</t>
   </si>
   <si>
     <t xml:space="preserve">Hall 4</t>
   </si>
   <si>
+    <t xml:space="preserve">Bed3 Curtain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dining Room Upwards firing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitchen spot nearest dining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oval Light over informal dining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Bed WIR near lounge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hall 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powder ceiling</t>
+  </si>
+  <si>
+    <t>Shower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitchen bench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bed3 Downlight near window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lounge sconce</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bed2 Ceiling corner</t>
   </si>
   <si>
-    <t xml:space="preserve">Bed2 Ceiling near door</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Bed WIR near lounge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Bed</t>
-  </si>
-  <si>
     <t xml:space="preserve">Laundry near exterior</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitchen near laundry</t>
-  </si>
-  <si>
-    <t>Kitchen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Bed WIR near bath</t>
+    <t xml:space="preserve">Bed3 Sconce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallway Disc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Bath ceiling strip</t>
   </si>
   <si>
     <t xml:space="preserve">Lounge ceiling near bed</t>
   </si>
   <si>
-    <t xml:space="preserve">Bed3 Ceiling near door</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed3 Sconce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master toilet ceiling</t>
+    <t xml:space="preserve">kitchen spot nearest hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Bed Niche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hall 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lounge celining near bookshelf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitchen near fridge</t>
+  </si>
+  <si>
+    <t>Mystery</t>
   </si>
   <si>
     <t>BBQ</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitchen near fridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lounge celining near bookshelf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Powder ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oval Light over informal dining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed3 Curtain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed3 Downlight near window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hallway Disc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kitchen bench</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Bath sconce</t>
-  </si>
-  <si>
     <t xml:space="preserve">Master Toilet window</t>
   </si>
   <si>
-    <t xml:space="preserve">Bath2 soap holder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lounge sconce</t>
-  </si>
-  <si>
-    <t>Mystery</t>
-  </si>
-  <si>
-    <t>Shower</t>
-  </si>
-  <si>
     <t xml:space="preserve">Master bed bar near bath</t>
   </si>
   <si>
-    <t xml:space="preserve">kitchen spot nearest hall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dining Room Upwards firing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hall 3 (wide angle)</t>
+    <t xml:space="preserve">Dining Room Down firing</t>
   </si>
   <si>
     <t xml:space="preserve">Bed2 Curtain</t>
   </si>
   <si>
-    <t xml:space="preserve">Dining Room Down firing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Bed Niche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bed2 Sconce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kitchen spot nearest dining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hall 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master Bath ceiling strip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hall 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Front deck under-deck</t>
   </si>
   <si>
+    <t xml:space="preserve">Laundry cabinet top</t>
+  </si>
+  <si>
     <t xml:space="preserve">Smiley Face</t>
   </si>
   <si>
+    <t>w</t>
+  </si>
+  <si>
     <t xml:space="preserve">Has manual switch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front Door Light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broken Driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laundry cabinet top</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Has No Driver yet</t>
   </si>
   <si>
     <t xml:space="preserve">Back Deck light</t>
@@ -619,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -627,8 +657,11 @@
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2017,8 +2050,11 @@
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -2034,7 +2070,7 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -2045,7 +2081,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -2056,7 +2092,7 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -2064,10 +2100,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
@@ -2078,7 +2114,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -2086,10 +2122,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -2100,10 +2136,10 @@
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
@@ -2119,7 +2155,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2147,37 +2183,37 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -2188,7 +2224,7 @@
     </row>
     <row r="2" ht="14.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -2216,7 +2252,7 @@
     </row>
     <row r="3" ht="14.25">
       <c r="A3" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
@@ -2249,10 +2285,10 @@
     </row>
     <row r="4" ht="14.25">
       <c r="A4" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2282,10 +2318,10 @@
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2330,10 +2366,10 @@
     </row>
     <row r="7" ht="14.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2363,10 +2399,10 @@
     </row>
     <row r="8" ht="14.25">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2396,10 +2432,10 @@
     </row>
     <row r="9" ht="14.25">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2427,7 +2463,7 @@
     </row>
     <row r="10" ht="14.25">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -2457,9 +2493,11 @@
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="5"/>
+      <c r="A11" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2479,9 +2517,11 @@
       </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12"/>
-      <c r="B12" t="s">
-        <v>45</v>
+      <c r="A12" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -2501,7 +2541,7 @@
     </row>
     <row r="13" ht="14.25">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
@@ -2545,10 +2585,10 @@
     </row>
     <row r="15" ht="14.25">
       <c r="A15" s="5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -2574,10 +2614,10 @@
     </row>
     <row r="16" ht="14.25">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2603,10 +2643,10 @@
     </row>
     <row r="17" ht="14.25">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2632,10 +2672,10 @@
     </row>
     <row r="18" ht="14.25">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2662,10 +2702,10 @@
     </row>
     <row r="19" ht="14.25">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2695,10 +2735,10 @@
     </row>
     <row r="20" ht="14.25">
       <c r="A20" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" s="5">
         <v>1</v>
@@ -2726,10 +2766,10 @@
     </row>
     <row r="21" ht="14.25">
       <c r="A21" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2754,7 +2794,7 @@
     </row>
     <row r="22" ht="14.25">
       <c r="A22" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
@@ -2783,10 +2823,10 @@
     </row>
     <row r="23" ht="14.25">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2817,10 +2857,10 @@
     </row>
     <row r="24" ht="14.25">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2851,10 +2891,10 @@
     </row>
     <row r="25" ht="14.25">
       <c r="A25" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2886,10 +2926,10 @@
     </row>
     <row r="26" ht="14.25">
       <c r="A26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -2903,7 +2943,7 @@
       <c r="F26" s="6">
         <v>4</v>
       </c>
-      <c r="H26" s="7"/>
+      <c r="H26" s="8"/>
       <c r="J26" s="6"/>
       <c r="L26">
         <v>0.69840000000000002</v>
@@ -2935,10 +2975,10 @@
     </row>
     <row r="28" ht="14.25">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -2963,10 +3003,10 @@
     </row>
     <row r="29" ht="14.25">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2998,10 +3038,10 @@
     </row>
     <row r="30" ht="14.25">
       <c r="A30" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -3042,10 +3082,10 @@
     </row>
     <row r="32" ht="14.25">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -3071,7 +3111,7 @@
       <c r="J32" s="6">
         <v>4</v>
       </c>
-      <c r="K32" s="8"/>
+      <c r="K32" s="9"/>
       <c r="L32">
         <v>0.51468999999999998</v>
       </c>
@@ -3081,10 +3121,10 @@
     </row>
     <row r="33" ht="14.25">
       <c r="A33" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -3109,10 +3149,10 @@
     </row>
     <row r="34" ht="14.25">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -3142,10 +3182,10 @@
     </row>
     <row r="35" ht="14.25">
       <c r="A35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C35">
         <v>2</v>
@@ -3170,10 +3210,10 @@
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="3" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -3198,10 +3238,10 @@
     </row>
     <row r="37" ht="14.25">
       <c r="A37" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -3231,10 +3271,10 @@
     </row>
     <row r="38" ht="14.25">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -3263,268 +3303,252 @@
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-      <c r="D39">
-        <v>8</v>
-      </c>
-      <c r="E39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F39" s="6">
-        <v>1</v>
-      </c>
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10">
+        <v>2</v>
+      </c>
+      <c r="D39" s="10">
+        <v>7</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="5"/>
       <c r="H39" s="6"/>
       <c r="J39" s="6"/>
-      <c r="L39">
-        <v>0.42529</v>
-      </c>
-      <c r="M39">
-        <v>0.26057999999999998</v>
-      </c>
+      <c r="K39" t="s">
+        <v>119</v>
+      </c>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" t="s">
-        <v>116</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40">
-        <v>2</v>
-      </c>
-      <c r="D40">
-        <v>9</v>
-      </c>
-      <c r="E40" t="s">
-        <v>36</v>
-      </c>
-      <c r="F40" s="6">
-        <v>2</v>
-      </c>
-      <c r="G40" t="s">
-        <v>35</v>
-      </c>
-      <c r="H40" s="6">
-        <v>2</v>
-      </c>
+      <c r="A40" s="10"/>
+      <c r="B40" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="10">
+        <v>2</v>
+      </c>
+      <c r="D40" s="10">
+        <v>7</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="6"/>
       <c r="J40" s="6"/>
-      <c r="K40" s="5"/>
-      <c r="L40">
-        <v>0.41621999999999998</v>
-      </c>
-      <c r="M40">
-        <v>0.26050000000000001</v>
+      <c r="K40" t="s">
+        <v>121</v>
+      </c>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="41" ht="14.25">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F41" s="6">
-        <v>2</v>
-      </c>
-      <c r="G41" t="s">
-        <v>35</v>
-      </c>
-      <c r="H41" s="6">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H41" s="6"/>
       <c r="J41" s="6"/>
       <c r="L41">
-        <v>0.50692000000000004</v>
+        <v>0.42529</v>
       </c>
       <c r="M41">
-        <v>0.17923</v>
+        <v>0.26057999999999998</v>
       </c>
     </row>
     <row r="42" ht="14.25">
       <c r="A42" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" t="s">
-        <v>103</v>
+        <v>123</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
         <v>36</v>
       </c>
       <c r="F42" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" t="s">
         <v>35</v>
       </c>
       <c r="H42" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="6"/>
+      <c r="K42" s="5"/>
       <c r="L42">
-        <v>0.50693999999999995</v>
+        <v>0.41621999999999998</v>
       </c>
       <c r="M42">
-        <v>0.14723</v>
+        <v>0.26050000000000001</v>
       </c>
     </row>
     <row r="43" ht="14.25">
       <c r="A43" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F43" s="6">
         <v>2</v>
       </c>
       <c r="G43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H43" s="6">
-        <v>0</v>
-      </c>
-      <c r="I43"/>
+        <v>1</v>
+      </c>
       <c r="J43" s="6"/>
       <c r="L43">
-        <v>0.50670000000000004</v>
+        <v>0.50692000000000004</v>
       </c>
       <c r="M43">
-        <v>0.19731000000000001</v>
+        <v>0.17923</v>
       </c>
     </row>
     <row r="44" ht="14.25">
       <c r="A44" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F44" s="6">
-        <v>1</v>
-      </c>
-      <c r="H44" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="G44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H44" s="6">
+        <v>0</v>
+      </c>
       <c r="J44" s="6"/>
       <c r="L44">
-        <v>0.40845999999999999</v>
+        <v>0.50693999999999995</v>
       </c>
       <c r="M44">
-        <v>0.13980999999999999</v>
+        <v>0.14723</v>
       </c>
     </row>
     <row r="45" ht="14.25">
       <c r="A45" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
       </c>
       <c r="F45" s="6">
-        <v>3</v>
-      </c>
-      <c r="H45" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="G45" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0</v>
+      </c>
+      <c r="I45"/>
       <c r="J45" s="6"/>
       <c r="L45">
-        <v>0.36752000000000001</v>
+        <v>0.50670000000000004</v>
       </c>
       <c r="M45">
-        <v>8.9700000000000005e-03</v>
+        <v>0.19731000000000001</v>
       </c>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>103</v>
+      <c r="A46" t="s">
+        <v>127</v>
+      </c>
+      <c r="B46" t="s">
+        <v>118</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
         <v>15</v>
       </c>
-      <c r="E46" t="s">
-        <v>36</v>
-      </c>
       <c r="F46" s="6">
-        <v>0</v>
-      </c>
-      <c r="G46" t="s">
-        <v>35</v>
-      </c>
-      <c r="H46" s="6">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H46" s="6"/>
       <c r="J46" s="6"/>
       <c r="L46">
-        <v>0.51524000000000003</v>
+        <v>0.40845999999999999</v>
       </c>
       <c r="M46">
-        <v>0.15916</v>
+        <v>0.13980999999999999</v>
       </c>
     </row>
     <row r="47" ht="14.25">
       <c r="A47" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C47">
         <v>2</v>
       </c>
       <c r="D47">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -3532,830 +3556,860 @@
       <c r="F47" s="6">
         <v>3</v>
       </c>
-      <c r="G47" t="s">
-        <v>34</v>
-      </c>
-      <c r="H47" s="6">
-        <v>2</v>
-      </c>
+      <c r="H47" s="6"/>
       <c r="J47" s="6"/>
       <c r="L47">
-        <v>0.2072</v>
+        <v>0.36752000000000001</v>
       </c>
       <c r="M47">
-        <v>0.16113</v>
+        <v>8.9700000000000005e-03</v>
       </c>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" t="s">
-        <v>124</v>
-      </c>
-      <c r="B48" t="s">
-        <v>103</v>
+      <c r="A48" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="D48">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F48" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H48" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J48" s="6"/>
       <c r="L48">
-        <v>0.24321000000000001</v>
+        <v>0.51524000000000003</v>
       </c>
       <c r="M48">
-        <v>0.16125</v>
+        <v>0.15916</v>
       </c>
     </row>
     <row r="49" ht="14.25">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F49" s="6">
         <v>3</v>
       </c>
-      <c r="H49" s="6"/>
+      <c r="G49" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="6">
+        <v>2</v>
+      </c>
       <c r="J49" s="6"/>
       <c r="L49">
-        <v>0.1807</v>
+        <v>0.2072</v>
       </c>
       <c r="M49">
-        <v>0.18845000000000001</v>
+        <v>0.16113</v>
       </c>
     </row>
     <row r="50" ht="14.25">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C50">
         <v>2</v>
       </c>
       <c r="D50">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F50" s="6">
         <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H50" s="6">
         <v>2</v>
       </c>
       <c r="J50" s="6"/>
-      <c r="K50" s="5"/>
       <c r="L50">
-        <v>0.26860000000000001</v>
+        <v>0.24321000000000001</v>
       </c>
       <c r="M50">
-        <v>0.33315</v>
+        <v>0.16125</v>
       </c>
     </row>
     <row r="51" ht="14.25">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F51" s="6">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="6">
-        <v>1</v>
-      </c>
-      <c r="I51" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="H51" s="6"/>
       <c r="J51" s="6"/>
-      <c r="K51" s="5"/>
       <c r="L51">
-        <v>0.84330000000000005</v>
+        <v>0.1807</v>
       </c>
       <c r="M51">
-        <v>0.73365999999999998</v>
+        <v>0.18845000000000001</v>
       </c>
     </row>
     <row r="52" ht="14.25">
       <c r="A52" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="C52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F52" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H52" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52" s="6"/>
+      <c r="K52" s="5"/>
       <c r="L52">
-        <v>0.73740000000000006</v>
+        <v>0.26860000000000001</v>
       </c>
       <c r="M52">
-        <v>0.76132</v>
+        <v>0.33315</v>
       </c>
     </row>
     <row r="53" ht="14.25">
       <c r="A53" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>5</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F53" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H53" s="6">
-        <v>2</v>
-      </c>
-      <c r="J53" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="I53" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" s="6">
+        <v>2</v>
+      </c>
       <c r="L53">
-        <v>0.72833999999999999</v>
+        <v>0.84330000000000005</v>
       </c>
       <c r="M53">
-        <v>0.80681000000000003</v>
+        <v>0.73365999999999998</v>
       </c>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
+      <c r="A54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" t="s">
+        <v>84</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F54" s="6">
         <v>0</v>
       </c>
-      <c r="H54" s="6"/>
+      <c r="G54" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="6">
+        <v>0</v>
+      </c>
       <c r="J54" s="6"/>
-      <c r="K54"/>
+      <c r="K54" t="s">
+        <v>136</v>
+      </c>
       <c r="L54">
-        <v>0.72909999999999997</v>
+        <v>0.73740000000000006</v>
       </c>
       <c r="M54">
-        <v>0.86794000000000004</v>
+        <v>0.76132</v>
       </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="5" t="s">
-        <v>131</v>
+      <c r="A55" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F55" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H55" s="6"/>
       <c r="J55" s="6"/>
-      <c r="K55"/>
+      <c r="K55" s="10" t="s">
+        <v>138</v>
+      </c>
       <c r="L55">
+        <v>0.72833999999999999</v>
+      </c>
+      <c r="M55">
+        <v>0.80681000000000003</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56">
+        <v>3</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="6">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H56" s="6">
+        <v>1</v>
+      </c>
+      <c r="I56" s="5"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="3"/>
+      <c r="L56">
+        <v>0.72909999999999997</v>
+      </c>
+      <c r="M56">
+        <v>0.86794000000000004</v>
+      </c>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C57" s="10">
+        <v>3</v>
+      </c>
+      <c r="D57" s="10">
+        <v>3</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="10">
+        <v>3</v>
+      </c>
+      <c r="D58" s="10">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="6">
+        <v>3</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H58" s="6">
+        <v>3</v>
+      </c>
+      <c r="I58" s="10"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="L58">
         <v>0.77481999999999995</v>
       </c>
-      <c r="M55">
+      <c r="M58">
         <v>0.86514000000000002</v>
       </c>
     </row>
-    <row r="56" ht="14.25">
-      <c r="A56" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C56">
-        <v>3</v>
-      </c>
-      <c r="D56">
-        <v>18</v>
-      </c>
-      <c r="E56" t="s">
-        <v>37</v>
-      </c>
-      <c r="F56" s="6">
-        <v>0</v>
-      </c>
-      <c r="G56" t="s">
-        <v>7</v>
-      </c>
-      <c r="H56" s="6">
-        <v>2</v>
-      </c>
-      <c r="J56" s="6"/>
-      <c r="L56">
-        <v>0.77488000000000001</v>
-      </c>
-      <c r="M56">
-        <v>0.80406999999999995</v>
-      </c>
-    </row>
-    <row r="57" ht="14.25">
-      <c r="A57" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57">
-        <v>3</v>
-      </c>
-      <c r="D57">
-        <v>28</v>
-      </c>
-      <c r="E57" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" s="6">
-        <v>0</v>
-      </c>
-      <c r="G57" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="6">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6"/>
-      <c r="L57">
-        <v>0.82133999999999996</v>
-      </c>
-      <c r="M57">
-        <v>0.86787999999999998</v>
-      </c>
-    </row>
-    <row r="58" ht="14.25">
-      <c r="A58" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B58" t="s">
-        <v>136</v>
-      </c>
-      <c r="C58">
-        <v>3</v>
-      </c>
-      <c r="D58">
+    <row r="59" ht="14.25">
+      <c r="A59" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B59" t="s">
+        <v>144</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59">
         <v>4</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E59" t="s">
         <v>17</v>
-      </c>
-      <c r="F58" s="6">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="L58">
-        <v>0.82123000000000002</v>
-      </c>
-      <c r="M58">
-        <v>0.80496999999999996</v>
-      </c>
-    </row>
-    <row r="59" ht="14.25">
-      <c r="A59" t="s">
-        <v>137</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59">
-        <v>3</v>
-      </c>
-      <c r="D59">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>37</v>
       </c>
       <c r="F59" s="6">
         <v>0</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
-      </c>
-      <c r="H59" s="6">
-        <v>2</v>
-      </c>
+      <c r="H59" s="6"/>
       <c r="J59" s="6"/>
-      <c r="K59"/>
       <c r="L59">
-        <v>2.503e-02</v>
+        <v>0.77488000000000001</v>
       </c>
       <c r="M59">
-        <v>0.16669999999999999</v>
+        <v>0.80406999999999995</v>
       </c>
     </row>
     <row r="60" ht="14.25">
       <c r="A60" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B60" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="6">
         <v>0</v>
       </c>
       <c r="H60" s="6"/>
       <c r="J60" s="6"/>
-      <c r="K60"/>
+      <c r="K60" s="5"/>
       <c r="L60">
-        <v>3.5139999999999998e-02</v>
+        <v>0.82133999999999996</v>
       </c>
       <c r="M60">
-        <v>0.19055</v>
+        <v>0.86787999999999998</v>
       </c>
     </row>
     <row r="61" ht="14.25">
       <c r="A61" t="s">
-        <v>139</v>
-      </c>
-      <c r="B61" t="s">
-        <v>11</v>
+        <v>146</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="5">
+        <v>6</v>
+      </c>
+      <c r="E61" t="s">
         <v>5</v>
       </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
       <c r="F61" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H61" s="6"/>
       <c r="J61" s="6"/>
-      <c r="K61" s="5"/>
+      <c r="K61" s="10"/>
       <c r="L61">
-        <v>7.6139999999999999e-02</v>
+        <v>0.82123000000000002</v>
       </c>
       <c r="M61">
-        <v>0.23055999999999999</v>
+        <v>0.80496999999999996</v>
       </c>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" t="s">
-        <v>140</v>
-      </c>
-      <c r="B62" t="s">
-        <v>11</v>
+      <c r="A62" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F62" s="6">
-        <v>1</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H62" s="6">
+        <v>2</v>
+      </c>
+      <c r="I62" s="10"/>
       <c r="J62" s="6"/>
+      <c r="K62"/>
       <c r="L62">
-        <v>6.6379999999999995e-02</v>
+        <v>2.503e-02</v>
       </c>
       <c r="M62">
-        <v>9.6750000000000003e-02</v>
+        <v>0.16669999999999999</v>
       </c>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" t="s">
-        <v>141</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>5</v>
+      <c r="A63" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
-      <c r="D63" s="3">
-        <v>6</v>
+      <c r="D63">
+        <v>8</v>
       </c>
       <c r="E63" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="F63" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6"/>
       <c r="J63" s="6"/>
       <c r="K63"/>
       <c r="L63">
-        <v>1.18e-02</v>
+        <v>3.5139999999999998e-02</v>
       </c>
       <c r="M63">
-        <v>9.1800000000000007e-02</v>
+        <v>0.19055</v>
       </c>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" t="s">
-        <v>142</v>
-      </c>
-      <c r="B64" t="s">
-        <v>78</v>
+      <c r="A64" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
-      <c r="D64" s="5">
-        <v>53</v>
+      <c r="D64">
+        <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="F64" s="6">
-        <v>1</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>7</v>
+      </c>
+      <c r="H64" s="6">
+        <v>2</v>
+      </c>
       <c r="J64" s="6"/>
+      <c r="K64" s="10"/>
       <c r="L64">
-        <v>5.3019999999999998e-02</v>
+        <v>7.6139999999999999e-02</v>
       </c>
       <c r="M64">
-        <v>0.10556</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="s">
-        <v>143</v>
+        <v>0.23055999999999999</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" t="s">
+        <v>151</v>
       </c>
       <c r="B65" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F65" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="6"/>
       <c r="J65" s="6"/>
       <c r="L65">
-        <v>3.6209999999999999e-02</v>
+        <v>6.6379999999999995e-02</v>
       </c>
       <c r="M65">
-        <v>0.10184</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>144</v>
-      </c>
-      <c r="B66" t="s">
-        <v>80</v>
+        <v>9.6750000000000003e-02</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>105</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F66" s="6">
-        <v>0</v>
-      </c>
-      <c r="H66" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="G66" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="6">
+        <v>2</v>
+      </c>
       <c r="J66" s="6"/>
+      <c r="K66"/>
       <c r="L66">
-        <v>8.5819999999999994e-02</v>
+        <v>1.18e-02</v>
       </c>
       <c r="M66">
-        <v>0.22975000000000001</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C67" s="5">
-        <v>3</v>
-      </c>
-      <c r="D67" s="5">
-        <v>21</v>
+        <v>9.1800000000000007e-02</v>
+      </c>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="A67" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F67" s="6">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5"/>
+        <v>2</v>
+      </c>
       <c r="H67" s="6"/>
-      <c r="I67" s="5"/>
       <c r="J67" s="6"/>
-      <c r="K67" s="5"/>
       <c r="L67">
-        <v>0.14049</v>
+        <v>5.3019999999999998e-02</v>
       </c>
       <c r="M67">
-        <v>0.16084000000000001</v>
+        <v>0.10556</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E68" t="s">
         <v>13</v>
       </c>
       <c r="F68" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="H68" s="6">
-        <v>1</v>
-      </c>
-      <c r="J68" s="6"/>
+        <v>3</v>
+      </c>
+      <c r="I68" t="s">
+        <v>8</v>
+      </c>
+      <c r="J68" s="6">
+        <v>4</v>
+      </c>
       <c r="L68">
-        <v>0.11122</v>
+        <v>3.6209999999999999e-02</v>
       </c>
       <c r="M68">
-        <v>0.16103000000000001</v>
+        <v>0.10184</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>147</v>
-      </c>
-      <c r="B69" t="s">
-        <v>11</v>
+        <v>155</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69">
+        <v>15</v>
+      </c>
+      <c r="E69" t="s">
         <v>13</v>
       </c>
-      <c r="E69" t="s">
-        <v>11</v>
-      </c>
       <c r="F69" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6"/>
       <c r="J69" s="6"/>
       <c r="L69">
-        <v>0.12304</v>
+        <v>8.5819999999999994e-02</v>
       </c>
       <c r="M69">
-        <v>0.2888</v>
+        <v>0.22975000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>11</v>
+        <v>156</v>
+      </c>
+      <c r="B70" t="s">
+        <v>81</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E70" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F70" s="6">
-        <v>0</v>
-      </c>
-      <c r="G70"/>
-      <c r="H70" s="6"/>
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>37</v>
+      </c>
+      <c r="H70" s="6">
+        <v>1</v>
+      </c>
       <c r="J70" s="6"/>
-      <c r="K70" s="5"/>
       <c r="L70">
-        <v>0.18509999999999999</v>
+        <v>0.14049</v>
       </c>
       <c r="M70">
-        <v>0.49329000000000001</v>
+        <v>0.16084000000000001</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
-        <v>149</v>
-      </c>
-      <c r="B71" t="s">
-        <v>101</v>
+      <c r="A71" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E71" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F71" s="6">
         <v>0</v>
       </c>
-      <c r="G71"/>
-      <c r="H71" s="6"/>
+      <c r="G71" t="s">
+        <v>7</v>
+      </c>
+      <c r="H71" s="6">
+        <v>2</v>
+      </c>
       <c r="J71" s="6"/>
       <c r="L71">
-        <v>0.16732</v>
+        <v>0.11122</v>
       </c>
       <c r="M71">
-        <v>0.34770000000000001</v>
+        <v>0.16103000000000001</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>150</v>
+      <c r="A72" t="s">
+        <v>158</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72">
+        <v>20</v>
+      </c>
+      <c r="E72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="6">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
         <v>23</v>
       </c>
-      <c r="E72" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="6">
-        <v>0</v>
-      </c>
-      <c r="H72" s="6"/>
+      <c r="H72" s="6">
+        <v>4</v>
+      </c>
       <c r="J72" s="6"/>
       <c r="L72">
-        <v>0.40573999999999999</v>
+        <v>0.12304</v>
       </c>
       <c r="M72">
-        <v>0.40015000000000001</v>
+        <v>0.2888</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
-        <v>151</v>
-      </c>
-      <c r="B73" t="s">
+      <c r="A73" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C73" s="5">
+        <v>3</v>
+      </c>
+      <c r="D73" s="5">
+        <v>21</v>
+      </c>
+      <c r="E73" t="s">
+        <v>22</v>
+      </c>
+      <c r="F73" s="6">
+        <v>0</v>
+      </c>
+      <c r="G73" s="3"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="5"/>
+      <c r="L73">
+        <v>0.18509999999999999</v>
+      </c>
+      <c r="M73">
+        <v>0.49329000000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
-      <c r="D73">
-        <v>0</v>
-      </c>
-      <c r="E73" t="s">
-        <v>5</v>
-      </c>
-      <c r="F73" s="6">
-        <v>1</v>
-      </c>
-      <c r="G73" t="s">
-        <v>7</v>
-      </c>
-      <c r="H73" s="6">
-        <v>1</v>
-      </c>
-      <c r="I73" t="s">
-        <v>37</v>
-      </c>
-      <c r="J73" s="6">
-        <v>2</v>
-      </c>
-      <c r="L73">
-        <v>0.30718000000000001</v>
-      </c>
-      <c r="M73">
-        <v>0.36860999999999999</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>152</v>
-      </c>
-      <c r="B74" t="s">
-        <v>5</v>
-      </c>
       <c r="C74">
         <v>3</v>
       </c>
-      <c r="D74" s="5">
-        <v>57</v>
+      <c r="D74">
+        <v>22</v>
       </c>
       <c r="E74" t="s">
         <v>5</v>
@@ -4363,324 +4417,321 @@
       <c r="F74" s="6">
         <v>3</v>
       </c>
+      <c r="G74"/>
       <c r="H74" s="6"/>
       <c r="J74" s="6"/>
-      <c r="K74" s="5"/>
       <c r="L74">
+        <v>0.16732</v>
+      </c>
+      <c r="M74">
+        <v>0.34770000000000001</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B75" t="s">
+        <v>144</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>23</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="L75">
+        <v>0.40573999999999999</v>
+      </c>
+      <c r="M75">
+        <v>0.40015000000000001</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>25</v>
+      </c>
+      <c r="E76" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="6">
+        <v>0</v>
+      </c>
+      <c r="G76" s="10"/>
+      <c r="H76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="5"/>
+      <c r="L76">
+        <v>0.30718000000000001</v>
+      </c>
+      <c r="M76">
+        <v>0.36860999999999999</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" s="10">
+        <v>3</v>
+      </c>
+      <c r="D77" s="10">
+        <v>26</v>
+      </c>
+      <c r="E77" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" s="6">
+        <v>1</v>
+      </c>
+      <c r="G77" s="10"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="10"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="10"/>
+      <c r="L77">
         <v>0.28232000000000002</v>
       </c>
-      <c r="M74">
+      <c r="M77">
         <v>0.74499000000000004</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>153</v>
-      </c>
-      <c r="B75" t="s">
-        <v>94</v>
-      </c>
-      <c r="C75">
-        <v>3</v>
-      </c>
-      <c r="D75">
-        <v>3</v>
-      </c>
-      <c r="E75" t="s">
-        <v>25</v>
-      </c>
-      <c r="F75" s="6">
-        <v>3</v>
-      </c>
-      <c r="G75" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="6">
-        <v>3</v>
-      </c>
-      <c r="I75"/>
-      <c r="J75" s="6"/>
-      <c r="K75"/>
-      <c r="L75">
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78">
+        <v>27</v>
+      </c>
+      <c r="E78" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="6">
+        <v>0</v>
+      </c>
+      <c r="G78"/>
+      <c r="H78" s="6"/>
+      <c r="I78"/>
+      <c r="J78" s="6"/>
+      <c r="K78"/>
+      <c r="L78">
         <v>0.50866</v>
       </c>
-      <c r="M75">
+      <c r="M78">
         <v>0.23694000000000001</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>154</v>
-      </c>
-      <c r="B76" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76">
-        <v>3</v>
-      </c>
-      <c r="D76">
-        <v>26</v>
-      </c>
-      <c r="E76" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="6">
-        <v>1</v>
-      </c>
-      <c r="G76"/>
-      <c r="H76" s="6"/>
-      <c r="I76"/>
-      <c r="J76" s="6"/>
-      <c r="K76"/>
-      <c r="L76">
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" t="s">
+        <v>84</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79">
+        <v>28</v>
+      </c>
+      <c r="E79" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" s="6">
+        <v>0</v>
+      </c>
+      <c r="G79" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="6">
+        <v>0</v>
+      </c>
+      <c r="I79"/>
+      <c r="J79" s="6"/>
+      <c r="K79"/>
+      <c r="L79">
         <v>0.50695999999999997</v>
       </c>
-      <c r="M76">
+      <c r="M79">
         <v>0.2215</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C77">
-        <v>3</v>
-      </c>
-      <c r="D77">
-        <v>45</v>
-      </c>
-      <c r="F77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="J77" s="6"/>
-      <c r="L77">
-        <v>0.49284</v>
-      </c>
-      <c r="M77">
-        <v>0.23652999999999999</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>156</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78">
-        <v>3</v>
-      </c>
-      <c r="D78">
-        <v>22</v>
-      </c>
-      <c r="E78" t="s">
-        <v>5</v>
-      </c>
-      <c r="F78" s="6">
-        <v>3</v>
-      </c>
-      <c r="H78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="L78">
-        <v>0.55464000000000002</v>
-      </c>
-      <c r="M78">
-        <v>0.35977999999999999</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C79">
-        <v>3</v>
-      </c>
-      <c r="D79">
-        <v>58</v>
-      </c>
-      <c r="E79" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" s="6">
-        <v>1</v>
-      </c>
-      <c r="H79" s="6"/>
-      <c r="J79" s="6"/>
-      <c r="L79">
-        <v>0.50151999999999997</v>
-      </c>
-      <c r="M79">
-        <v>0.36008000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="C80">
         <v>3</v>
       </c>
-      <c r="D80">
-        <v>35</v>
+      <c r="D80" s="10">
+        <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F80" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H80" s="6"/>
       <c r="J80" s="6"/>
       <c r="L80">
-        <v>0.51034000000000002</v>
+        <v>0.49284</v>
       </c>
       <c r="M80">
-        <v>0.44258999999999998</v>
+        <v>0.23652999999999999</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="s">
-        <v>159</v>
+      <c r="A81" t="s">
+        <v>167</v>
       </c>
       <c r="B81" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C81">
         <v>3</v>
       </c>
       <c r="D81">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E81" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F81" s="6">
-        <v>3</v>
-      </c>
-      <c r="G81" t="s">
-        <v>17</v>
-      </c>
-      <c r="H81" s="6">
-        <v>3</v>
-      </c>
-      <c r="I81" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="6">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G81" s="10"/>
+      <c r="H81" s="6"/>
+      <c r="J81" s="6"/>
       <c r="L81">
-        <v>0.58986000000000005</v>
+        <v>0.55464000000000002</v>
       </c>
       <c r="M81">
-        <v>0.48066999999999999</v>
+        <v>0.35977999999999999</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>101</v>
+      <c r="A82" t="s">
+        <v>168</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>5</v>
       </c>
       <c r="C82">
         <v>3</v>
       </c>
       <c r="D82">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F82" s="6">
-        <v>2</v>
-      </c>
-      <c r="G82" t="s">
-        <v>27</v>
-      </c>
-      <c r="H82" s="6">
-        <v>2</v>
-      </c>
-      <c r="I82"/>
+        <v>0</v>
+      </c>
+      <c r="G82" s="10"/>
+      <c r="H82" s="6"/>
       <c r="J82" s="6"/>
+      <c r="K82" s="5"/>
       <c r="L82">
-        <v>0.57837000000000005</v>
+        <v>0.50151999999999997</v>
       </c>
       <c r="M82">
-        <v>0.38973000000000002</v>
+        <v>0.36008000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E83" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F83" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6"/>
       <c r="J83" s="6"/>
-      <c r="K83" s="3"/>
+      <c r="K83" s="10"/>
       <c r="L83">
-        <v>0.41831000000000002</v>
+        <v>0.51034000000000002</v>
       </c>
       <c r="M83">
-        <v>0.61895999999999995</v>
+        <v>0.44258999999999998</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B84" t="s">
-        <v>136</v>
+      <c r="A84" t="s">
+        <v>170</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="C84">
         <v>3</v>
       </c>
       <c r="D84">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E84" t="s">
         <v>13</v>
       </c>
-      <c r="F84" s="7">
-        <v>2</v>
+      <c r="F84" s="6">
+        <v>4</v>
       </c>
       <c r="H84" s="6"/>
       <c r="J84" s="6"/>
       <c r="L84">
-        <v>0.73336999999999997</v>
+        <v>0.58986000000000005</v>
       </c>
       <c r="M84">
-        <v>0.37383</v>
+        <v>0.48066999999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C85">
         <v>3</v>
@@ -4694,317 +4745,400 @@
       <c r="F85" s="6">
         <v>0</v>
       </c>
+      <c r="G85"/>
       <c r="H85" s="6"/>
+      <c r="I85"/>
       <c r="J85" s="6"/>
-      <c r="K85"/>
+      <c r="K85" s="10"/>
       <c r="L85">
-        <v>0.69293000000000005</v>
+        <v>0.57837000000000005</v>
       </c>
       <c r="M85">
-        <v>0.71189999999999998</v>
+        <v>0.38973000000000002</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>164</v>
-      </c>
-      <c r="B86" t="s">
-        <v>24</v>
+        <v>172</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="C86">
         <v>3</v>
       </c>
       <c r="D86">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E86" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F86" s="6">
         <v>1</v>
       </c>
-      <c r="H86" s="6"/>
+      <c r="G86" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="6">
+        <v>4</v>
+      </c>
       <c r="J86" s="6"/>
+      <c r="K86"/>
       <c r="L86">
-        <v>0.75165000000000004</v>
+        <v>0.41831000000000002</v>
       </c>
       <c r="M86">
-        <v>0.72365000000000002</v>
+        <v>0.61895999999999995</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>165</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>136</v>
+        <v>173</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="C87">
         <v>3</v>
       </c>
       <c r="D87">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E87" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="6">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="F87" s="8">
+        <v>0</v>
       </c>
       <c r="H87" s="6"/>
       <c r="J87" s="6"/>
       <c r="L87">
-        <v>0.65059</v>
+        <v>0.73336999999999997</v>
       </c>
       <c r="M87">
-        <v>0.69833999999999996</v>
+        <v>0.37383</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s">
-        <v>166</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>101</v>
+      <c r="A88" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="C88">
         <v>3</v>
       </c>
-      <c r="D88">
-        <v>38</v>
+      <c r="D88" s="10">
+        <v>43</v>
       </c>
       <c r="E88" t="s">
         <v>17</v>
       </c>
       <c r="F88" s="6">
-        <v>1</v>
-      </c>
-      <c r="G88" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="6">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="J88" s="6"/>
+      <c r="K88"/>
+      <c r="L88">
+        <v>0.69293000000000005</v>
+      </c>
+      <c r="M88">
+        <v>0.71189999999999998</v>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="s">
-        <v>167</v>
-      </c>
-      <c r="B89" t="s">
-        <v>5</v>
+      <c r="A89" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="C89">
         <v>3</v>
       </c>
       <c r="D89">
-        <v>33</v>
-      </c>
-      <c r="E89" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="6">
-        <v>0</v>
-      </c>
-      <c r="G89"/>
+        <v>45</v>
+      </c>
+      <c r="F89" s="6"/>
       <c r="H89" s="6"/>
       <c r="J89" s="6"/>
-      <c r="K89" s="5"/>
+      <c r="L89">
+        <v>0.75165000000000004</v>
+      </c>
+      <c r="M89">
+        <v>0.72365000000000002</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>168</v>
-      </c>
-      <c r="B90" t="s">
-        <v>101</v>
+        <v>176</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="C90">
         <v>3</v>
       </c>
-      <c r="D90">
-        <v>20</v>
+      <c r="D90" s="5">
+        <v>53</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F90" s="6">
         <v>1</v>
       </c>
-      <c r="G90" t="s">
-        <v>23</v>
-      </c>
-      <c r="H90" s="6">
-        <v>4</v>
-      </c>
+      <c r="H90" s="6"/>
       <c r="J90" s="6"/>
       <c r="L90">
-        <v>6.6949999999999996e-02</v>
+        <v>0.65059</v>
       </c>
       <c r="M90">
-        <v>0.34520000000000001</v>
+        <v>0.69833999999999996</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
+      <c r="A91" t="s">
+        <v>177</v>
+      </c>
+      <c r="B91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91" s="5">
+        <v>57</v>
+      </c>
       <c r="E91" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F91" s="6">
         <v>3</v>
       </c>
-      <c r="G91" s="5"/>
+      <c r="G91"/>
       <c r="H91" s="6"/>
-      <c r="I91" s="5"/>
       <c r="J91" s="6"/>
+      <c r="K91" s="5"/>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>101</v>
+      <c r="A92" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C92">
+        <v>3</v>
+      </c>
+      <c r="D92">
+        <v>58</v>
       </c>
       <c r="E92" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F92" s="6">
         <v>1</v>
       </c>
-      <c r="G92" t="s">
-        <v>30</v>
-      </c>
-      <c r="H92" s="6">
-        <v>0</v>
-      </c>
+      <c r="G92"/>
+      <c r="H92" s="6"/>
       <c r="J92" s="6"/>
-      <c r="K92" s="5" t="s">
-        <v>171</v>
-      </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="s">
-        <v>172</v>
+      <c r="A93" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="B93" t="s">
-        <v>78</v>
+        <v>144</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93">
+        <v>60</v>
       </c>
       <c r="E93" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F93" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H93" s="6"/>
       <c r="J93" s="6"/>
-      <c r="K93" t="s">
-        <v>173</v>
+      <c r="L93">
+        <v>6.6949999999999996e-02</v>
+      </c>
+      <c r="M93">
+        <v>0.34520000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>174</v>
-      </c>
-      <c r="B94" t="s">
-        <v>83</v>
-      </c>
-      <c r="C94"/>
-      <c r="D94" s="3"/>
+        <v>180</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94">
+        <v>62</v>
+      </c>
       <c r="E94" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="6">
+        <v>2</v>
+      </c>
+      <c r="H94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="5"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" t="s">
+        <v>27</v>
+      </c>
+      <c r="F95" s="6">
+        <v>3</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="6"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="10"/>
+      <c r="D96" s="5"/>
+      <c r="E96" t="s">
         <v>18</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F96" s="6">
         <v>0</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G96" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H94" s="6">
+      <c r="H96" s="6">
         <v>0</v>
       </c>
-      <c r="I94" s="5"/>
-      <c r="J94" s="6"/>
-      <c r="K94" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>176</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E95" t="s">
+      <c r="I96" s="5"/>
+      <c r="J96" s="6"/>
+      <c r="K96"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97" t="s">
+        <v>27</v>
+      </c>
+      <c r="F97" s="6">
+        <v>1</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J97" s="6"/>
+      <c r="K97" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>186</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E98" t="s">
         <v>14</v>
       </c>
-      <c r="F95" s="6">
-        <v>1</v>
-      </c>
-      <c r="H95" s="6"/>
-      <c r="J95" s="6"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>177</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="F98" s="6">
+        <v>1</v>
+      </c>
+      <c r="H98" s="6"/>
+      <c r="J98" s="6"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>187</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E99" t="s">
         <v>23</v>
       </c>
-      <c r="F96" s="6">
-        <v>3</v>
-      </c>
-      <c r="H96" s="6"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="L96">
+      <c r="F99" s="6">
+        <v>3</v>
+      </c>
+      <c r="H99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="L99">
         <v>4.9509999999999998e-02</v>
       </c>
-      <c r="M96">
+      <c r="M99">
         <v>0.14158000000000001</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-    </row>
-    <row r="98">
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-    </row>
-    <row r="104">
-      <c r="G104" s="3"/>
+    <row r="100">
+      <c r="A100" s="3"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+    </row>
+    <row r="101">
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+    </row>
+    <row r="107">
+      <c r="G107" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K101">
-    <sortState ref="A2:K101" columnSort="0">
+  <autoFilter ref="A1:K104">
+    <sortState ref="A2:K104" columnSort="0">
       <sortCondition sortBy="value" descending="0" ref="C2:C101"/>
       <sortCondition sortBy="value" descending="0" ref="D2:D101"/>
     </sortState>
   </autoFilter>
   <dataValidations count="7" disablePrompts="0">
-    <dataValidation sqref="E10:E96" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+    <dataValidation sqref="E10:E99" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
       <formula1>'Switch Positions'!$A$2:$A$29</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E96" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+    <dataValidation sqref="E2:E99" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
       <formula1>'Switch Positions'!$A$2:$A$29</formula1>
     </dataValidation>
     <dataValidation sqref="G10:G33" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
@@ -5013,13 +5147,13 @@
     <dataValidation sqref="G2:G33" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
       <formula1>'Switch Positions'!$A$2:$A$29</formula1>
     </dataValidation>
-    <dataValidation sqref="G35:G94" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+    <dataValidation sqref="G35:G97" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
       <formula1>'Switch Positions'!$A$2:$A$29</formula1>
     </dataValidation>
-    <dataValidation sqref="I10:I94" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+    <dataValidation sqref="I10:I97" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
       <formula1>'Switch Positions'!$A$2:$A$29</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I94" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+    <dataValidation sqref="I2:I97" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
       <formula1>'Switch Positions'!$A$2:$A$29</formula1>
     </dataValidation>
   </dataValidations>
@@ -5036,16 +5170,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B1" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
